--- a/resources/templates/timetable.xlsx
+++ b/resources/templates/timetable.xlsx
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">One lecture per row, from row 5 down. Times like 8:00 or 2:00 pm. Leave the day empty to repeat the day above.</t>
+          <t xml:space="preserve">One lecture per row, from row 5 down. Times like 8:00 or 2:00 pm. Leave the day empty to repeat the day above; title, lecturer and venue can stay empty.</t>
         </is>
       </c>
     </row>
